--- a/data/t-tests--class_scores.xlsx
+++ b/data/t-tests--class_scores.xlsx
@@ -2775,7 +2775,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: pre/post test scores for two teaching methods.</t>
+          <t>WHAT IS CAPTURED: pre/post test scores for two teaching methods (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
